--- a/report_forms/037_patient_handover_form--report_forms.xlsx
+++ b/report_forms/037_patient_handover_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -638,12 +638,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'mr'}</t>
+          <t>mr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Mr'}</t>
+          <t>Mr</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'mrs'}</t>
+          <t>mrs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Mrs'}</t>
+          <t>Mrs</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'dr'}</t>
+          <t>dr</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Dr'}</t>
+          <t>Dr</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'miss'}</t>
+          <t>miss</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Miss'}</t>
+          <t>Miss</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'mrs'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Mrs'}</t>
+          <t>Ms</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'ms'}</t>
+          <t>rev</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Ms'}</t>
+          <t>Rev</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>patient_details_choices</t>
+          <t>patient_gender_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'rev'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Rev'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -790,29 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>patient_gender_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'value':_'female'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
